--- a/excels/placements.xlsx
+++ b/excels/placements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BE5727-E04B-4A96-9D8A-117F62496F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1ED0086-7D3E-4EEC-99BA-C5480435252D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="placements" sheetId="1" r:id="rId1"/>
